--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -7041,10 +7041,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121152378</v>
+        <v>121152376</v>
       </c>
       <c r="B62" t="n">
-        <v>91967</v>
+        <v>91957</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7057,21 +7057,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693067</v>
+        <v>692911</v>
       </c>
       <c r="R62" t="n">
-        <v>7318190</v>
+        <v>7318360</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121152376</v>
+        <v>121149662</v>
       </c>
       <c r="B63" t="n">
-        <v>91947</v>
+        <v>91973</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7164,25 +7164,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692911</v>
+        <v>692816</v>
       </c>
       <c r="R63" t="n">
-        <v>7318360</v>
+        <v>7318452</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121152377</v>
+        <v>121152378</v>
       </c>
       <c r="B64" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693094</v>
+        <v>693067</v>
       </c>
       <c r="R64" t="n">
-        <v>7318220</v>
+        <v>7318190</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7374,10 +7374,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121149662</v>
+        <v>121152377</v>
       </c>
       <c r="B65" t="n">
-        <v>91963</v>
+        <v>91977</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7386,25 +7386,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692816</v>
+        <v>693094</v>
       </c>
       <c r="R65" t="n">
-        <v>7318452</v>
+        <v>7318220</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7448,12 +7448,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">

--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -7041,10 +7041,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121152376</v>
+        <v>121149662</v>
       </c>
       <c r="B62" t="n">
-        <v>91957</v>
+        <v>91973</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7053,25 +7053,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692911</v>
+        <v>692816</v>
       </c>
       <c r="R62" t="n">
-        <v>7318360</v>
+        <v>7318452</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7115,12 +7115,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7152,10 +7152,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121149662</v>
+        <v>121152377</v>
       </c>
       <c r="B63" t="n">
-        <v>91973</v>
+        <v>91977</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7164,25 +7164,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692816</v>
+        <v>693094</v>
       </c>
       <c r="R63" t="n">
-        <v>7318452</v>
+        <v>7318220</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121152378</v>
+        <v>121152376</v>
       </c>
       <c r="B64" t="n">
-        <v>91977</v>
+        <v>91957</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7279,21 +7279,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693067</v>
+        <v>692911</v>
       </c>
       <c r="R64" t="n">
-        <v>7318190</v>
+        <v>7318360</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121152377</v>
+        <v>121152378</v>
       </c>
       <c r="B65" t="n">
         <v>91977</v>
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693094</v>
+        <v>693067</v>
       </c>
       <c r="R65" t="n">
-        <v>7318220</v>
+        <v>7318190</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>

--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -7041,10 +7041,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121149662</v>
+        <v>121152378</v>
       </c>
       <c r="B62" t="n">
-        <v>91973</v>
+        <v>91989</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7053,25 +7053,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692816</v>
+        <v>693067</v>
       </c>
       <c r="R62" t="n">
-        <v>7318452</v>
+        <v>7318190</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7115,12 +7115,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7155,7 +7155,7 @@
         <v>121152377</v>
       </c>
       <c r="B63" t="n">
-        <v>91977</v>
+        <v>91989</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121152376</v>
+        <v>121149662</v>
       </c>
       <c r="B64" t="n">
-        <v>91957</v>
+        <v>91985</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7275,25 +7275,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692911</v>
+        <v>692816</v>
       </c>
       <c r="R64" t="n">
-        <v>7318360</v>
+        <v>7318452</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7374,10 +7374,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121152378</v>
+        <v>121152376</v>
       </c>
       <c r="B65" t="n">
-        <v>91977</v>
+        <v>91969</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7390,21 +7390,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693067</v>
+        <v>692911</v>
       </c>
       <c r="R65" t="n">
-        <v>7318190</v>
+        <v>7318360</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>

--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -7044,7 +7044,7 @@
         <v>121152378</v>
       </c>
       <c r="B62" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>121152377</v>
       </c>
       <c r="B63" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121149662</v>
+        <v>121152376</v>
       </c>
       <c r="B64" t="n">
-        <v>91985</v>
+        <v>91970</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7275,25 +7275,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692816</v>
+        <v>692911</v>
       </c>
       <c r="R64" t="n">
-        <v>7318452</v>
+        <v>7318360</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7374,10 +7374,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121152376</v>
+        <v>121149662</v>
       </c>
       <c r="B65" t="n">
-        <v>91969</v>
+        <v>91986</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7386,25 +7386,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692911</v>
+        <v>692816</v>
       </c>
       <c r="R65" t="n">
-        <v>7318360</v>
+        <v>7318452</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7448,12 +7448,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">

--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -7041,10 +7041,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121152378</v>
+        <v>121152377</v>
       </c>
       <c r="B62" t="n">
-        <v>91990</v>
+        <v>91993</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693067</v>
+        <v>693094</v>
       </c>
       <c r="R62" t="n">
-        <v>7318190</v>
+        <v>7318220</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121152377</v>
+        <v>121149662</v>
       </c>
       <c r="B63" t="n">
-        <v>91990</v>
+        <v>91989</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7164,25 +7164,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693094</v>
+        <v>692816</v>
       </c>
       <c r="R63" t="n">
-        <v>7318220</v>
+        <v>7318452</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7266,7 +7266,7 @@
         <v>121152376</v>
       </c>
       <c r="B64" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7374,10 +7374,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121149662</v>
+        <v>121152378</v>
       </c>
       <c r="B65" t="n">
-        <v>91986</v>
+        <v>91993</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7386,25 +7386,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692816</v>
+        <v>693067</v>
       </c>
       <c r="R65" t="n">
-        <v>7318452</v>
+        <v>7318190</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7448,12 +7448,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">

--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -7041,10 +7041,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121152377</v>
+        <v>121152376</v>
       </c>
       <c r="B62" t="n">
-        <v>91993</v>
+        <v>91973</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7057,21 +7057,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693094</v>
+        <v>692911</v>
       </c>
       <c r="R62" t="n">
-        <v>7318220</v>
+        <v>7318360</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121149662</v>
+        <v>121152378</v>
       </c>
       <c r="B63" t="n">
-        <v>91989</v>
+        <v>91993</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7164,25 +7164,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692816</v>
+        <v>693067</v>
       </c>
       <c r="R63" t="n">
-        <v>7318452</v>
+        <v>7318190</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121152376</v>
+        <v>121152377</v>
       </c>
       <c r="B64" t="n">
-        <v>91973</v>
+        <v>91993</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7279,21 +7279,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6055</v>
+        <v>4365</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692911</v>
+        <v>693094</v>
       </c>
       <c r="R64" t="n">
-        <v>7318360</v>
+        <v>7318220</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7374,10 +7374,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121152378</v>
+        <v>121149662</v>
       </c>
       <c r="B65" t="n">
-        <v>91993</v>
+        <v>91989</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7386,25 +7386,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693067</v>
+        <v>692816</v>
       </c>
       <c r="R65" t="n">
-        <v>7318190</v>
+        <v>7318452</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7448,12 +7448,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">

--- a/artfynd/A 46285-2020 artfynd.xlsx
+++ b/artfynd/A 46285-2020 artfynd.xlsx
@@ -7041,10 +7041,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121152376</v>
+        <v>121152378</v>
       </c>
       <c r="B62" t="n">
-        <v>91973</v>
+        <v>91993</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7057,21 +7057,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6055</v>
+        <v>4365</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692911</v>
+        <v>693067</v>
       </c>
       <c r="R62" t="n">
-        <v>7318360</v>
+        <v>7318190</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121152378</v>
+        <v>121152376</v>
       </c>
       <c r="B63" t="n">
-        <v>91993</v>
+        <v>91973</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7168,21 +7168,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693067</v>
+        <v>692911</v>
       </c>
       <c r="R63" t="n">
-        <v>7318190</v>
+        <v>7318360</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
